--- a/raw_data/ice_off_dates20240918.xlsx
+++ b/raw_data/ice_off_dates20240918.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Gagers/Documents/Thesis and Lab/Ice Phenology Project/Ice_Pheno/Input_Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaga3666/repos/Ice_Pheno/raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A206A7-20F8-ED4D-BD5B-3A8EB705BF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A72BCB44-30CF-8A4F-B597-E3550278A170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8140" yWindow="1600" windowWidth="19720" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.33203125" customWidth="1"/>
@@ -588,6 +588,14 @@
         <v>2025</v>
       </c>
     </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
+        <v>46132</v>
+      </c>
+      <c r="C15">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
